--- a/assignment-1/docs/RTM.xlsx
+++ b/assignment-1/docs/RTM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FA26\MMA301\MMA301_Assignment_1\MMA301_Assignment_1\assignment-1\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FA26\MMA301\MMA301_Assignment_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2B67DF-EA38-4602-9DE8-83B471AE82E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7587EE-774D-4A6B-9CA7-1DB12E465CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="492" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -924,7 +924,7 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>57</v>
       </c>
@@ -959,7 +959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>67</v>
       </c>
@@ -994,7 +994,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>77</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>86</v>
       </c>
